--- a/backend/uploads/Component_Update.xlsx
+++ b/backend/uploads/Component_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bavkumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29337C70-ED1B-4DF7-BB0F-995FF7B0484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760A7244-01F2-4F7B-8102-F4EB45E619C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D7C8339F-CE35-41E0-B12D-490C8E1B8DD2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>Page Path</t>
   </si>
@@ -47,22 +47,25 @@
     <t>Component Name</t>
   </si>
   <si>
-    <t>Property</t>
-  </si>
-  <si>
     <t>New Value</t>
   </si>
   <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>/content/we-retail/ca/en/men/jcr:content/root/responsivegrid/title</t>
-  </si>
-  <si>
-    <t>jcr:title</t>
-  </si>
-  <si>
-    <t>Ram trucks 2026</t>
+    <t>/content/we-retail/ca/en/men</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Field Name</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>Title Component 1</t>
+  </si>
+  <si>
+    <t>Title Component 2</t>
   </si>
 </sst>
 </file>
@@ -133,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -147,6 +150,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095186FD-B50C-4C2F-9860-0CD9A30DCEA8}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.1796875" customWidth="1"/>
@@ -490,7 +494,7 @@
     <col min="4" max="4" width="44.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -498,39 +502,56 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="1"/>
+    <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
